--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/IDAHO_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/IDAHO_2014.xlsx
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C63">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C163">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C458">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C493">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C658">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C691">
